--- a/output/candidates.xlsx
+++ b/output/candidates.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>291593</v>
+        <v>291535</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
@@ -645,22 +645,22 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>81070</v>
+        <v>81157.67</v>
       </c>
       <c r="S2" t="n">
-        <v>79002</v>
+        <v>79036</v>
       </c>
       <c r="T2" t="n">
-        <v>103653.5</v>
+        <v>103740</v>
       </c>
       <c r="U2" t="n">
-        <v>35903</v>
+        <v>35993</v>
       </c>
       <c r="V2" t="n">
-        <v>2.887</v>
+        <v>2.8822</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5821</v>
+        <v>0.5816</v>
       </c>
       <c r="X2" t="n">
         <v>74.25</v>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>441935</v>
+        <v>441849</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -734,22 +734,22 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>334650.8</v>
+        <v>335358.2</v>
       </c>
       <c r="S3" t="n">
-        <v>421189</v>
+        <v>421522</v>
       </c>
       <c r="T3" t="n">
-        <v>456214</v>
+        <v>457115</v>
       </c>
       <c r="U3" t="n">
-        <v>304260</v>
+        <v>304919</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4994</v>
+        <v>1.4991</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1389</v>
+        <v>0.1392</v>
       </c>
       <c r="X3" t="n">
         <v>73.25</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>434288</v>
+        <v>434325</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -825,25 +825,25 @@
         <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>376894</v>
+        <v>386009.5</v>
       </c>
       <c r="S4" t="n">
-        <v>376894</v>
+        <v>386009.5</v>
       </c>
       <c r="T4" t="n">
-        <v>322572</v>
+        <v>324225</v>
       </c>
       <c r="U4" t="n">
-        <v>431216</v>
+        <v>447794</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7481</v>
+        <v>0.724</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6269</v>
+        <v>0.6182</v>
       </c>
       <c r="X4" t="n">
-        <v>68.05</v>
+        <v>67.56</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jeyeon_lee</t>
+          <t>hyeim__j</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jeyeon_lee/</t>
+          <t>https://www.instagram.com/hyeim__j/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -878,22 +878,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>이제연</t>
+          <t>정 혜임</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>228583</v>
+        <v>197745</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>변호사 / rosewpdus@naver.com</t>
+          <t>hyeim@cableagency.co.kr</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>0.75</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1667</v>
+        <v>0.3333</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -902,37 +902,37 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P5" t="n">
         <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>131157.75</v>
+        <v>59805.67</v>
       </c>
       <c r="S5" t="n">
-        <v>143320</v>
+        <v>56070.5</v>
       </c>
       <c r="T5" t="n">
-        <v>102092</v>
+        <v>43282</v>
       </c>
       <c r="U5" t="n">
-        <v>218355</v>
+        <v>63110.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4676</v>
+        <v>0.6858</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3392</v>
+        <v>0.4038</v>
       </c>
       <c r="X5" t="n">
-        <v>64.44</v>
+        <v>66.63</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
@@ -944,12 +944,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hyeim__j</t>
+          <t>jeyeon_lee</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hyeim__j/</t>
+          <t>https://www.instagram.com/jeyeon_lee/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>정 혜임</t>
+          <t>이제연</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>197772</v>
+        <v>228639</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>hyeim@cableagency.co.kr</t>
+          <t>변호사 / rosewpdus@naver.com</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>0.75</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3333</v>
+        <v>0.1667</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -991,37 +991,37 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>56848.5</v>
+        <v>131718.5</v>
       </c>
       <c r="S6" t="n">
-        <v>55687</v>
+        <v>143943</v>
       </c>
       <c r="T6" t="n">
-        <v>30808</v>
+        <v>102787.33</v>
       </c>
       <c r="U6" t="n">
-        <v>62056.6</v>
+        <v>218512</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4965</v>
+        <v>0.4704</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4234</v>
+        <v>0.3386</v>
       </c>
       <c r="X6" t="n">
-        <v>62.85</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>197912</v>
+        <v>197868</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1093,25 +1093,25 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>15086.29</v>
+        <v>16381.71</v>
       </c>
       <c r="S7" t="n">
-        <v>7409</v>
+        <v>8372</v>
       </c>
       <c r="T7" t="n">
-        <v>5721</v>
+        <v>5934</v>
       </c>
       <c r="U7" t="n">
-        <v>16647.17</v>
+        <v>18123</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3437</v>
+        <v>0.3274</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2547</v>
+        <v>0.2367</v>
       </c>
       <c r="X7" t="n">
-        <v>58.12</v>
+        <v>57.8</v>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>96238</v>
+        <v>96244</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1182,25 +1182,25 @@
         <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>105945.5</v>
+        <v>114921</v>
       </c>
       <c r="S8" t="n">
-        <v>105945.5</v>
+        <v>114921</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>105945.5</v>
+        <v>114921</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>56.08</v>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>348333</v>
+        <v>348133</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>206522.5</v>
+        <v>207584</v>
       </c>
       <c r="S9" t="n">
-        <v>206522.5</v>
+        <v>207584</v>
       </c>
       <c r="T9" t="n">
-        <v>206522.5</v>
+        <v>207584</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.751</v>
+        <v>0.7509</v>
       </c>
       <c r="X9" t="n">
         <v>54.92</v>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>393261</v>
+        <v>395234</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1364,13 +1364,13 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>56493</v>
+        <v>59850</v>
       </c>
       <c r="S10" t="n">
-        <v>56493</v>
+        <v>59850</v>
       </c>
       <c r="T10" t="n">
-        <v>56493</v>
+        <v>59850</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>4.7863</v>
+        <v>4.6332</v>
       </c>
       <c r="X10" t="n">
         <v>54.78</v>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>339345</v>
+        <v>339258</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1455,22 +1455,22 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>40854.14</v>
+        <v>44124</v>
       </c>
       <c r="S11" t="n">
-        <v>34000</v>
+        <v>34702</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>40854.14</v>
+        <v>44124</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2557</v>
+        <v>0.2427</v>
       </c>
       <c r="X11" t="n">
         <v>54.26</v>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>133167</v>
+        <v>133862</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1544,22 +1544,22 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>735435.67</v>
+        <v>741920.5</v>
       </c>
       <c r="S12" t="n">
-        <v>107188</v>
+        <v>380552.5</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>735435.67</v>
+        <v>741920.5</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1535</v>
+        <v>0.1487</v>
       </c>
       <c r="X12" t="n">
         <v>54.08</v>
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>393686</v>
+        <v>394436</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1633,25 +1633,25 @@
         <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>435259</v>
+        <v>440409</v>
       </c>
       <c r="S13" t="n">
-        <v>110549</v>
+        <v>111266</v>
       </c>
       <c r="T13" t="n">
-        <v>85531</v>
+        <v>88003</v>
       </c>
       <c r="U13" t="n">
-        <v>1134715</v>
+        <v>1145221</v>
       </c>
       <c r="V13" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4183</v>
+        <v>0.4253</v>
       </c>
       <c r="X13" t="n">
-        <v>53.76</v>
+        <v>53.79</v>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>128933</v>
+        <v>128982</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1723,22 +1723,22 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>495577</v>
+        <v>495847.33</v>
       </c>
       <c r="S14" t="n">
-        <v>493487</v>
+        <v>494008</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>495577</v>
+        <v>495847.33</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1567</v>
+        <v>0.1566</v>
       </c>
       <c r="X14" t="n">
         <v>53.08</v>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jjjohnnyeey</t>
+          <t>moi_bin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjjohnnyeey/</t>
+          <t>https://www.instagram.com/moi_bin/</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>lamuzes</t>
+          <t>2dumi</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1776,21 +1776,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>이지연</t>
+          <t>수 빈</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>335824</v>
+        <v>176965</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>지연하세요 안녕입니다
-jjjohnnyeey0113@gmail.com
-@ddang_kong_babyboy @kyunghee_university</t>
+          <t>한 번 사는 삶 사랑하고 살아가기</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1811,28 +1809,28 @@
         <v>12</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3649</v>
+        <v>20530</v>
       </c>
       <c r="S15" t="n">
-        <v>3649</v>
+        <v>20530</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3649</v>
+        <v>20530</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>27.6632</v>
+        <v>0.4559</v>
       </c>
       <c r="X15" t="n">
-        <v>52.25</v>
+        <v>52.28</v>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
@@ -1840,16 +1838,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>_seseung</t>
+          <t>jjjohnnyeey</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_seseung/</t>
+          <t>https://www.instagram.com/jjjohnnyeey/</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1859,7 +1857,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2dumi</t>
+          <t>lamuzes</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1867,13 +1865,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>박세승</t>
+          <t>이지연</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>280828</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>335793</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>지연하세요 안녕입니다
+jjjohnnyeey0113@gmail.com
+@ddang_kong_babyboy @kyunghee_university</t>
+        </is>
+      </c>
       <c r="J16" t="n">
         <v>0.75</v>
       </c>
@@ -1896,25 +1900,25 @@
         <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>86233</v>
+        <v>17726</v>
       </c>
       <c r="S16" t="n">
-        <v>86233</v>
+        <v>17726</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>86233</v>
+        <v>17726</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4829</v>
+        <v>2.2974</v>
       </c>
       <c r="X16" t="n">
         <v>52.25</v>
@@ -1925,16 +1929,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>moonjiwonn_</t>
+          <t>_seseung</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moonjiwonn_/</t>
+          <t>https://www.instagram.com/_seseung/</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1944,7 +1948,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>lamuzes</t>
+          <t>2dumi</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1952,17 +1956,13 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>문지원</t>
+          <t>박세승</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>188432</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>jiwonmoonn@gmail.com</t>
-        </is>
-      </c>
+        <v>280781</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
         <v>0.75</v>
       </c>
@@ -1976,34 +1976,34 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="O17" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>131044.67</v>
+        <v>86461</v>
       </c>
       <c r="S17" t="n">
-        <v>144461</v>
+        <v>86461</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>131044.67</v>
+        <v>86461</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4938</v>
+        <v>1.4839</v>
       </c>
       <c r="X17" t="n">
         <v>52.25</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gyoe_re</t>
+          <t>woo_yeol</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gyoe_re/</t>
+          <t>https://www.instagram.com/woo_yeol/</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>lamuzes</t>
+          <t>2dumi</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2041,18 +2041,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>한겨레</t>
+          <t>박우열 park wooyeol</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>496510</v>
+        <v>183699</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>John 3:16
-@hmode.co.kr Director
-hangyoere02@gmail.com
-[ 베흐트 X 한겨레 Market ] 8/10(월) 10:00 - 8/12(수) 23:59</t>
+          <t>woo_yeol@amazement.info</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -2068,37 +2065,37 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>23178.33</v>
+        <v>351921</v>
       </c>
       <c r="S18" t="n">
-        <v>20585</v>
+        <v>351921</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>23178.33</v>
+        <v>351921</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3294</v>
+        <v>2.41</v>
       </c>
       <c r="X18" t="n">
-        <v>51.25</v>
+        <v>52.25</v>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
@@ -2106,16 +2103,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>i0c0i</t>
+          <t>gyoe_re</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/i0c0i/</t>
+          <t>https://www.instagram.com/gyoe_re/</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2133,15 +2130,18 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>soal</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>407268</v>
+        <v>496513</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>@__0ii0__</t>
+          <t>John 3:16
+@hmode.co.kr Director
+hangyoere02@gmail.com
+[ 베흐트 X 한겨레 Market ] 8/10(월) 10:00 - 8/12(수) 23:59</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2157,34 +2157,34 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="P19" t="n">
         <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>99488.25</v>
+        <v>25735.5</v>
       </c>
       <c r="S19" t="n">
-        <v>80986</v>
+        <v>25735.5</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>99488.25</v>
+        <v>25735.5</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1678</v>
+        <v>0.3936</v>
       </c>
       <c r="X19" t="n">
         <v>51.25</v>
@@ -2195,16 +2195,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>im_hyeonzzu</t>
+          <t>i0c0i</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/im_hyeonzzu/</t>
+          <t>https://www.instagram.com/i0c0i/</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2dumi</t>
+          <t>lamuzes</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -2222,15 +2222,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>임현주</t>
+          <t>soal</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>361284</v>
+        <v>407109</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>hyeonzzuim@gmail.com</t>
+          <t>@__0ii0__</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -2243,37 +2243,37 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0.2</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="P20" t="n">
         <v>12</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>75900</v>
+        <v>102771.25</v>
       </c>
       <c r="S20" t="n">
-        <v>75900</v>
+        <v>83811</v>
       </c>
       <c r="T20" t="n">
-        <v>75900</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>102771.25</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.1635</v>
       </c>
       <c r="X20" t="n">
         <v>51.25</v>
@@ -2284,16 +2284,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>shin.seungg</t>
+          <t>im_hyeonzzu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shin.seungg/</t>
+          <t>https://www.instagram.com/im_hyeonzzu/</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>lamuzes</t>
+          <t>2dumi</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2311,15 +2311,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>신승용</t>
+          <t>임현주</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>319776</v>
+        <v>361204</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>✉️shin.seunggg@gmail.com.                                    @shin.seungg.doc</t>
+          <t>hyeonzzuim@gmail.com</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -2332,37 +2332,37 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P21" t="n">
         <v>12</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>677673</v>
+        <v>75924</v>
       </c>
       <c r="S21" t="n">
-        <v>677673</v>
+        <v>75924</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>75924</v>
       </c>
       <c r="U21" t="n">
-        <v>677673</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7573</v>
+        <v>0.57</v>
       </c>
       <c r="X21" t="n">
         <v>51.25</v>
@@ -2373,16 +2373,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pianolsy</t>
+          <t>shin.seungg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pianolsy/</t>
+          <t>https://www.instagram.com/shin.seungg/</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2dumi</t>
+          <t>lamuzes</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2400,18 +2400,15 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>이소영 (Lee Soyoung)</t>
+          <t>신승용</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>267148</v>
+        <v>319169</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>🎹📸🎞🎵🎙🎬💿👶🏻💕
-SoKuen 🎧🎵
-SKcouple 💛 🤰🏻🧑🏻‍🍼👶🏻📖
-👇🏻</t>
+          <t>✉️shin.seunggg@gmail.com.                                    @shin.seungg.doc</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -2436,25 +2433,25 @@
         <v>12</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>280085</v>
+        <v>693779</v>
       </c>
       <c r="S22" t="n">
-        <v>302358</v>
+        <v>693779</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>280085</v>
+        <v>693779</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.7419</v>
       </c>
       <c r="X22" t="n">
         <v>51.25</v>
@@ -2465,16 +2462,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>joohweylee</t>
+          <t>jiminlop</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/joohweylee/</t>
+          <t>https://www.instagram.com/jiminlop/</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2484,7 +2481,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>lamuzes</t>
+          <t>2dumi</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -2492,13 +2489,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>이주휘</t>
+          <t>김지민</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>115241</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>300154</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>지민롭❤️</t>
+        </is>
+      </c>
       <c r="J23" t="n">
         <v>0.75</v>
       </c>
@@ -2515,31 +2516,31 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P23" t="n">
         <v>12</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>761083.5</v>
+        <v>382296.2</v>
       </c>
       <c r="S23" t="n">
-        <v>761083.5</v>
+        <v>286144</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>761083.5</v>
+        <v>382296.2</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.4009</v>
+        <v>0.1233</v>
       </c>
       <c r="X23" t="n">
         <v>51.25</v>
@@ -2550,16 +2551,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>minzuyaa_</t>
+          <t>pianolsy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/minzuyaa_/</t>
+          <t>https://www.instagram.com/pianolsy/</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2569,7 +2570,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>lamuzes</t>
+          <t>2dumi</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -2577,15 +2578,18 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>김민주</t>
+          <t>이소영 (Lee Soyoung)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>89745</v>
+        <v>267133</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>📫  to.minzuyaa@gmail.com</t>
+          <t>🎹📸🎞🎵🎙🎬💿👶🏻💕
+SoKuen 🎧🎵
+SKcouple 💛 🤰🏻🧑🏻‍🍼👶🏻📖
+👇🏻</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2610,25 +2614,25 @@
         <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>576309</v>
+        <v>282984.67</v>
       </c>
       <c r="S24" t="n">
-        <v>576309</v>
+        <v>314024</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>576309</v>
+        <v>282984.67</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.1024</v>
       </c>
       <c r="X24" t="n">
         <v>51.25</v>
@@ -2639,16 +2643,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yoonmida</t>
+          <t>joohweylee</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yoonmida/</t>
+          <t>https://www.instagram.com/joohweylee/</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2658,7 +2662,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2dumi</t>
+          <t>lamuzes</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2666,22 +2670,18 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>지윤미</t>
+          <t>이주휘</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>484813</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>윤미다입니다</t>
-        </is>
-      </c>
+        <v>115228</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
         <v>0.75</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2699,28 +2699,28 @@
         <v>12</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>70255.42999999999</v>
+        <v>761211</v>
       </c>
       <c r="S25" t="n">
-        <v>41739</v>
+        <v>761211</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>70255.42999999999</v>
+        <v>761211</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.0116</v>
+        <v>0.4008</v>
       </c>
       <c r="X25" t="n">
-        <v>39.26</v>
+        <v>51.25</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
@@ -2728,16 +2728,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>juuuyeonn</t>
+          <t>minzuyaa_</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/juuuyeonn/</t>
+          <t>https://www.instagram.com/minzuyaa_/</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2dumi</t>
+          <t>lamuzes</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2755,17 +2755,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>주연🎀</t>
+          <t>김민주</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>200898</v>
+        <v>90040</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>피터앤웬디
-매주 화, 금 11am 신상 update 🚪⊹
-@peterandwendy.official</t>
+          <t>📫  to.minzuyaa@gmail.com</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -2781,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2793,25 +2791,25 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>586757</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>586757</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>586757</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.6062</v>
       </c>
       <c r="X26" t="n">
-        <v>39.25</v>
+        <v>51.25</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
@@ -2823,12 +2821,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>charles_is_loved</t>
+          <t>yoonmida</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/charles_is_loved/</t>
+          <t>https://www.instagram.com/yoonmida/</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2846,15 +2844,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>찰스</t>
+          <t>지윤미</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>475993</v>
+        <v>484863</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>그러나 그들 중 누구와도 나 자신을 바꾸지 않았을 것이다</t>
+          <t>윤미다입니다</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -2870,10 +2868,10 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P27" t="n">
         <v>12</v>
@@ -2882,25 +2880,25 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>57103</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>27503</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>57103</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>0.0424</v>
       </c>
       <c r="X27" t="n">
-        <v>38.25</v>
+        <v>44.2</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
@@ -2912,12 +2910,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>moi_bin</t>
+          <t>juuuyeonn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moi_bin/</t>
+          <t>https://www.instagram.com/juuuyeonn/</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2935,19 +2933,21 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>수 빈</t>
+          <t>주연🎀</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>176893</v>
+        <v>200880</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>한 번 사는 삶 사랑하고 살아가기</t>
+          <t>피터앤웬디
+매주 화, 금 11am 신상 update 🚪⊹
+@peterandwendy.official</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.751</v>
+        <v>0.75</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2959,13 +2959,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>36.29</v>
+        <v>39.25</v>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mingingyo</t>
+          <t>charles_is_loved</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mingingyo/</t>
+          <t>https://www.instagram.com/charles_is_loved/</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3024,16 +3024,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>신민규</t>
+          <t>찰스</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>288621</v>
+        <v>475932</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>@texture.ent @im.roxtar 
-minkyu.email@gmail.com</t>
+          <t>그러나 그들 중 누구와도 나 자신을 바꾸지 않았을 것이다</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -3049,16 +3048,16 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O29" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>12</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3079,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>36.25</v>
+        <v>38.25</v>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
@@ -3091,12 +3090,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yykkye</t>
+          <t>mingingyo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yykkye/</t>
+          <t>https://www.instagram.com/mingingyo/</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3114,13 +3113,18 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>강유경</t>
+          <t>신민규</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>260256</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
+        <v>288513</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>@texture.ent @im.roxtar 
+minkyu.email@gmail.com</t>
+        </is>
+      </c>
       <c r="J30" t="n">
         <v>0.75</v>
       </c>
@@ -3137,13 +3141,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P30" t="n">
         <v>12</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3176,12 +3180,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0west_</t>
+          <t>yykkye</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/0west_/</t>
+          <t>https://www.instagram.com/yykkye/</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3199,17 +3203,13 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>남영서</t>
+          <t>강유경</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>142217</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0west00000@gmail.com</t>
-        </is>
-      </c>
+        <v>260637</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
         <v>0.75</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>12</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
